--- a/data/Original_data/4_indicator_to_SDG.xlsx
+++ b/data/Original_data/4_indicator_to_SDG.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\State_SDG\Github\SDG_Interactions-driven-by-Urban_Typologies\data\Original_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uflorida-my.sharepoint.com/personal/genhong_gao_ufl_edu/Documents/Documents/PhD/PhD Programs/SDG/2_cities SDGs 082024/Statistical Analysis/Final_Data_082025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8939B3DE-7D28-4ECA-B463-2CA44830F3BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="146" documentId="11_F25DC773A252ABDACC1048C371DE6ECC5BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03073BD5-CFF7-4B1F-8786-9C20830EA3F8}"/>
   <bookViews>
-    <workbookView xWindow="3072" yWindow="3072" windowWidth="15648" windowHeight="11316" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="14856" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -92,169 +92,169 @@
     <t>SDG16</t>
   </si>
   <si>
-    <t>G1.1</t>
-  </si>
-  <si>
-    <t>G1.2</t>
-  </si>
-  <si>
-    <t>G1.3</t>
-  </si>
-  <si>
-    <t>G1.4</t>
-  </si>
-  <si>
-    <t>G1.5</t>
-  </si>
-  <si>
-    <t>G2.1</t>
-  </si>
-  <si>
-    <t>G2.4</t>
-  </si>
-  <si>
-    <t>G3.1</t>
-  </si>
-  <si>
-    <t>G3.2</t>
-  </si>
-  <si>
-    <t>G3.4</t>
-  </si>
-  <si>
-    <t>G3.6</t>
-  </si>
-  <si>
-    <t>G3.7</t>
-  </si>
-  <si>
-    <t>G3.8</t>
-  </si>
-  <si>
-    <t>G3.9</t>
-  </si>
-  <si>
-    <t>G4.2</t>
-  </si>
-  <si>
-    <t>G4.3</t>
-  </si>
-  <si>
-    <t>G4.4</t>
-  </si>
-  <si>
-    <t>G4.5</t>
-  </si>
-  <si>
-    <t>G5.1</t>
-  </si>
-  <si>
-    <t>G5.2</t>
-  </si>
-  <si>
-    <t>G6.1</t>
-  </si>
-  <si>
-    <t>G6.3</t>
-  </si>
-  <si>
-    <t>G6.4</t>
-  </si>
-  <si>
-    <t>G7.1</t>
-  </si>
-  <si>
-    <t>G7.2</t>
-  </si>
-  <si>
-    <t>G7.3</t>
-  </si>
-  <si>
-    <t>G8.1</t>
-  </si>
-  <si>
-    <t>G8.2</t>
-  </si>
-  <si>
-    <t>G8.3</t>
-  </si>
-  <si>
-    <t>G9.1</t>
-  </si>
-  <si>
-    <t>G9.2</t>
-  </si>
-  <si>
-    <t>G9.3</t>
-  </si>
-  <si>
-    <t>G10.2</t>
-  </si>
-  <si>
-    <t>G10.3</t>
-  </si>
-  <si>
-    <t>G10.5</t>
-  </si>
-  <si>
-    <t>G10.7</t>
-  </si>
-  <si>
-    <t>G10.8</t>
-  </si>
-  <si>
-    <t>G11.1</t>
-  </si>
-  <si>
-    <t>G11.2</t>
-  </si>
-  <si>
-    <t>G11.3</t>
-  </si>
-  <si>
-    <t>G11.4</t>
-  </si>
-  <si>
-    <t>G11.5</t>
-  </si>
-  <si>
-    <t>G12.1</t>
-  </si>
-  <si>
-    <t>G12.3</t>
-  </si>
-  <si>
-    <t>G12.4</t>
-  </si>
-  <si>
-    <t>G13.1</t>
-  </si>
-  <si>
-    <t>G13.2</t>
-  </si>
-  <si>
-    <t>G13.3</t>
-  </si>
-  <si>
-    <t>G15.1</t>
-  </si>
-  <si>
-    <t>G15.4</t>
-  </si>
-  <si>
-    <t>G16.1</t>
-  </si>
-  <si>
-    <t>G16.2</t>
-  </si>
-  <si>
-    <t>G16.5</t>
-  </si>
-  <si>
-    <t>G2.3</t>
-  </si>
-  <si>
-    <t>G5.4</t>
+    <t>SDG1.1</t>
+  </si>
+  <si>
+    <t>SDG1.2</t>
+  </si>
+  <si>
+    <t>SDG1.3</t>
+  </si>
+  <si>
+    <t>SDG1.4</t>
+  </si>
+  <si>
+    <t>SDG1.5</t>
+  </si>
+  <si>
+    <t>SDG2.1</t>
+  </si>
+  <si>
+    <t>SDG2.3</t>
+  </si>
+  <si>
+    <t>SDG2.4</t>
+  </si>
+  <si>
+    <t>SDG3.1</t>
+  </si>
+  <si>
+    <t>SDG3.2</t>
+  </si>
+  <si>
+    <t>SDG3.4</t>
+  </si>
+  <si>
+    <t>SDG3.6</t>
+  </si>
+  <si>
+    <t>SDG3.7</t>
+  </si>
+  <si>
+    <t>SDG3.8</t>
+  </si>
+  <si>
+    <t>SDG3.9</t>
+  </si>
+  <si>
+    <t>SDG4.2</t>
+  </si>
+  <si>
+    <t>SDG4.3</t>
+  </si>
+  <si>
+    <t>SDG4.4</t>
+  </si>
+  <si>
+    <t>SDG4.5</t>
+  </si>
+  <si>
+    <t>SDG5.1</t>
+  </si>
+  <si>
+    <t>SDG5.2</t>
+  </si>
+  <si>
+    <t>SDG5.4</t>
+  </si>
+  <si>
+    <t>SDG6.1</t>
+  </si>
+  <si>
+    <t>SDG6.3</t>
+  </si>
+  <si>
+    <t>SDG6.4</t>
+  </si>
+  <si>
+    <t>SDG7.1</t>
+  </si>
+  <si>
+    <t>SDG7.2</t>
+  </si>
+  <si>
+    <t>SDG7.3</t>
+  </si>
+  <si>
+    <t>SDG8.1</t>
+  </si>
+  <si>
+    <t>SDG8.2</t>
+  </si>
+  <si>
+    <t>SDG8.3</t>
+  </si>
+  <si>
+    <t>SDG9.1</t>
+  </si>
+  <si>
+    <t>SDG9.2</t>
+  </si>
+  <si>
+    <t>SDG9.3</t>
+  </si>
+  <si>
+    <t>SDG10.2</t>
+  </si>
+  <si>
+    <t>SDG10.3</t>
+  </si>
+  <si>
+    <t>SDG10.5</t>
+  </si>
+  <si>
+    <t>SDG10.7</t>
+  </si>
+  <si>
+    <t>SDG10.8</t>
+  </si>
+  <si>
+    <t>SDG11.1</t>
+  </si>
+  <si>
+    <t>SDG11.2</t>
+  </si>
+  <si>
+    <t>SDG11.3</t>
+  </si>
+  <si>
+    <t>SDG11.4</t>
+  </si>
+  <si>
+    <t>SDG11.5</t>
+  </si>
+  <si>
+    <t>SDG12.1</t>
+  </si>
+  <si>
+    <t>SDG12.3</t>
+  </si>
+  <si>
+    <t>SDG12.4</t>
+  </si>
+  <si>
+    <t>SDG13.1</t>
+  </si>
+  <si>
+    <t>SDG13.2</t>
+  </si>
+  <si>
+    <t>SDG13.3</t>
+  </si>
+  <si>
+    <t>SDG15.1</t>
+  </si>
+  <si>
+    <t>SDG15.4</t>
+  </si>
+  <si>
+    <t>SDG16.1</t>
+  </si>
+  <si>
+    <t>SDG16.2</t>
+  </si>
+  <si>
+    <t>SDG16.5</t>
   </si>
 </sst>
 </file>
@@ -653,7 +653,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
         <v>3</v>
@@ -661,7 +661,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
         <v>3</v>
@@ -669,7 +669,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
         <v>4</v>
@@ -677,7 +677,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B11" t="s">
         <v>4</v>
@@ -685,7 +685,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
         <v>4</v>
@@ -693,7 +693,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B13" t="s">
         <v>4</v>
@@ -701,7 +701,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B14" t="s">
         <v>4</v>
@@ -709,7 +709,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B15" t="s">
         <v>4</v>
@@ -717,7 +717,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B16" t="s">
         <v>4</v>
@@ -725,7 +725,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B17" t="s">
         <v>5</v>
@@ -733,7 +733,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B18" t="s">
         <v>5</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s">
         <v>5</v>
@@ -749,7 +749,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B20" t="s">
         <v>5</v>
@@ -757,7 +757,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B21" t="s">
         <v>6</v>
@@ -765,7 +765,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B22" t="s">
         <v>6</v>
@@ -773,7 +773,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="B23" t="s">
         <v>6</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B24" t="s">
         <v>7</v>
@@ -789,7 +789,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B25" t="s">
         <v>7</v>
@@ -797,7 +797,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B26" t="s">
         <v>7</v>
@@ -805,7 +805,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B27" t="s">
         <v>8</v>
@@ -813,7 +813,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B28" t="s">
         <v>8</v>
@@ -821,7 +821,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B29" t="s">
         <v>8</v>
@@ -829,7 +829,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B30" t="s">
         <v>9</v>
@@ -837,7 +837,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B31" t="s">
         <v>9</v>
@@ -845,7 +845,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B32" t="s">
         <v>9</v>
@@ -853,7 +853,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B33" t="s">
         <v>10</v>
@@ -861,7 +861,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B34" t="s">
         <v>10</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B35" t="s">
         <v>10</v>
@@ -877,7 +877,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B36" t="s">
         <v>11</v>
@@ -885,7 +885,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B37" t="s">
         <v>11</v>
@@ -893,7 +893,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B38" t="s">
         <v>11</v>
@@ -901,7 +901,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B39" t="s">
         <v>11</v>
@@ -909,7 +909,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B40" t="s">
         <v>11</v>
@@ -917,7 +917,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B41" t="s">
         <v>12</v>
@@ -925,7 +925,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B42" t="s">
         <v>12</v>
@@ -933,7 +933,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B43" t="s">
         <v>12</v>
@@ -941,7 +941,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B44" t="s">
         <v>12</v>
@@ -949,7 +949,7 @@
     </row>
     <row r="45" spans="1:2" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B45" t="s">
         <v>12</v>
@@ -957,7 +957,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
@@ -965,7 +965,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
@@ -973,7 +973,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B49" t="s">
         <v>14</v>
@@ -989,7 +989,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B50" t="s">
         <v>14</v>
@@ -997,7 +997,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B51" t="s">
         <v>14</v>
@@ -1005,7 +1005,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B52" t="s">
         <v>15</v>
@@ -1013,7 +1013,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B53" t="s">
         <v>15</v>
@@ -1021,7 +1021,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B54" t="s">
         <v>16</v>
@@ -1029,7 +1029,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B55" t="s">
         <v>16</v>
@@ -1037,7 +1037,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B56" t="s">
         <v>16</v>
